--- a/data/trans_bre/IP7_R-Estudios-trans_bre.xlsx
+++ b/data/trans_bre/IP7_R-Estudios-trans_bre.xlsx
@@ -660,42 +660,42 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>-6,0; 4,56</t>
+          <t>-6,04; 4,68</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>-6,99; 2,36</t>
+          <t>-6,62; 2,23</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>-3,94; 7,39</t>
+          <t>-3,97; 7,06</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>-8,68; 32,24</t>
+          <t>-7,53; 35,5</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>-73,61; 193,01</t>
+          <t>-73,35; 211,36</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>-88,49; 215,81</t>
+          <t>-91,2; 160,49</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>-100,0; —</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>-90,54; 1185,8</t>
+          <t>-89,12; 1890,0</t>
         </is>
       </c>
     </row>
@@ -760,42 +760,42 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>-3,25; 0,04</t>
+          <t>-3,54; -0,27</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>-1,53; 1,93</t>
+          <t>-1,41; 2,04</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>-1,78; 1,31</t>
+          <t>-1,8; 1,32</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>-0,69; 2,48</t>
+          <t>-0,58; 2,64</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>-80,29; 4,69</t>
+          <t>-79,59; -4,2</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>-46,18; 103,35</t>
+          <t>-44,28; 104,76</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>-56,7; 91,72</t>
+          <t>-55,3; 96,81</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>-34,06; 237,28</t>
+          <t>-30,05; 256,41</t>
         </is>
       </c>
     </row>
@@ -860,27 +860,27 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>-5,32; -0,8</t>
+          <t>-5,45; -0,84</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>-2,45; 1,49</t>
+          <t>-2,23; 1,44</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>-2,64; 0,63</t>
+          <t>-2,33; 0,69</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>-4,8; 1,57</t>
+          <t>-4,91; 1,41</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>-100,0; 73,13</t>
+          <t>-100,0; 44,35</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
@@ -895,7 +895,7 @@
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>-100,0; 165,04</t>
+          <t>-100,0; 169,41</t>
         </is>
       </c>
     </row>
@@ -960,42 +960,42 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>-3,3; -0,61</t>
+          <t>-3,19; -0,47</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>-1,47; 1,18</t>
+          <t>-1,5; 1,1</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>-1,38; 1,02</t>
+          <t>-1,45; 0,99</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>-0,96; 3,72</t>
+          <t>-0,95; 4,03</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>-74,76; -18,6</t>
+          <t>-73,96; -17,1</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>-47,95; 64,15</t>
+          <t>-48,06; 64,05</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>-51,57; 70,58</t>
+          <t>-54,2; 63,75</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>-34,71; 209,25</t>
+          <t>-37,77; 213,73</t>
         </is>
       </c>
     </row>
